--- a/zop_200.xlsx
+++ b/zop_200.xlsx
@@ -1,33 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matsv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matsv\Downloads\ZOP-TEST200\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1BA3CB-BB6E-4A07-B37F-454B84914866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVID 200" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -2224,7 +2212,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2600,7 +2588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4231,12 +4219,12 @@
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="3"/>
       <c r="B337" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B338" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
@@ -5885,14 +5873,14 @@
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B682" t="s">
+      <c r="A682" s="3"/>
+      <c r="B682" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B683" t="s">
         <v>491</v>
-      </c>
-    </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A683" s="3"/>
-      <c r="B683" s="4" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
